--- a/data/trans_orig/IP13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81563</t>
+          <t>81954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88875</t>
+          <t>88901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75665</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83587</t>
+          <t>84047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161074</t>
+          <t>160484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171488</t>
+          <t>171619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>28480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53043</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387547</t>
+          <t>387607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401431</t>
+          <t>401419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447447</t>
+          <t>447517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461774</t>
+          <t>461459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>840035</t>
+          <t>839961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>860411</t>
+          <t>859852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165207</t>
+          <t>165238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171963</t>
+          <t>171827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144299</t>
+          <t>144014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153522</t>
+          <t>153509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312559</t>
+          <t>311687</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323758</t>
+          <t>323607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27680</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54834</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79169</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>641158</t>
+          <t>641694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>657870</t>
+          <t>658371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>676293</t>
+          <t>676406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>694294</t>
+          <t>694353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1323826</t>
+          <t>1323365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1348161</t>
+          <t>1348648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19881</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81102</t>
+          <t>80872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88939</t>
+          <t>88904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>74042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82997</t>
+          <t>82458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158053</t>
+          <t>158269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169467</t>
+          <t>169562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>26414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43773</t>
+          <t>45703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46568</t>
+          <t>46037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71154</t>
+          <t>70787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418235</t>
+          <t>419674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434382</t>
+          <t>435449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447598</t>
+          <t>445668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>467273</t>
+          <t>464957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>871846</t>
+          <t>872213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896432</t>
+          <t>896963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11088</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153213</t>
+          <t>152714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162017</t>
+          <t>162276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161140</t>
+          <t>160795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>169771</t>
+          <t>169906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317791</t>
+          <t>317820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330675</t>
+          <t>330437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>50555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57488</t>
+          <t>58002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71140</t>
+          <t>70412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101699</t>
+          <t>100300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>660440</t>
+          <t>659627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>681251</t>
+          <t>680325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>692304</t>
+          <t>691790</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>714024</t>
+          <t>713707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1358275</t>
+          <t>1359674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1388834</t>
+          <t>1389562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53552</t>
+          <t>53360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62363</t>
+          <t>62660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>67948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118873</t>
+          <t>119030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126146</t>
+          <t>126283</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>32113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38326</t>
+          <t>38543</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58961</t>
+          <t>59805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440228</t>
+          <t>440177</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>455553</t>
+          <t>454766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455852</t>
+          <t>455886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>471969</t>
+          <t>471778</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>902064</t>
+          <t>901220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>922699</t>
+          <t>922482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155640</t>
+          <t>155029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166242</t>
+          <t>165782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174892</t>
+          <t>175245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184252</t>
+          <t>184353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>335197</t>
+          <t>334719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>348757</t>
+          <t>348181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>28561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>57615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>83620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>657200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>675904</t>
+          <t>675810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>700837</t>
+          <t>701725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720231</t>
+          <t>720800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1365671</t>
+          <t>1365595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1392094</t>
+          <t>1391600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45338</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48769</t>
+          <t>49166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97772</t>
+          <t>98274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109755</t>
+          <t>109680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>31219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39460</t>
+          <t>40706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40100</t>
+          <t>40922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65256</t>
+          <t>65039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428081</t>
+          <t>428475</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443677</t>
+          <t>444965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>477159</t>
+          <t>475913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495577</t>
+          <t>495314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911057</t>
+          <t>911274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>936213</t>
+          <t>935391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30606</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133385</t>
+          <t>132676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143762</t>
+          <t>143508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163321</t>
+          <t>163839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175949</t>
+          <t>175734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301570</t>
+          <t>301325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317064</t>
+          <t>317098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27946</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48681</t>
+          <t>48328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71000</t>
+          <t>71064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>103061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>615242</t>
+          <t>615595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635977</t>
+          <t>636115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701590</t>
+          <t>699766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>724706</t>
+          <t>723830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1322658</t>
+          <t>1322110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1354171</t>
+          <t>1354107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6052</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2761</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10692</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4726</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8913</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9380</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6052</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2798</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11347</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80793</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76153</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84084</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>86141</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>81954</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88901</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>81487</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>88841</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,8%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80793</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>75498</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84047</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160484</t>
+          <t>160721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171619</t>
+          <t>171143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21518</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15087</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29528</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>20879</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14668</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28480</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14376</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29107</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21518</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15532</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29474</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>32399</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53117</t>
+          <t>52396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>455473</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>447463</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>461904</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>596</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>395208</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>387607</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>401419</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>386980</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>401711</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,98%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>455473</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>447517</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>461459</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>839961</t>
+          <t>840682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859852</t>
+          <t>860679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8559</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4625</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14380</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4805</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2239</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8828</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9005</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8559</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149579</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143758</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153513</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>169261</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>165238</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>171827</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>165061</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>171798</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149579</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144014</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>153509</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311687</t>
+          <t>312207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323607</t>
+          <t>323453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36130</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27703</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46220</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30410</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22650</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>39327</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21917</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39561</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36130</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27621</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>45568</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54347</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79630</t>
+          <t>80101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>685844</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>675754</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>694271</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>650611</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>641694</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>658371</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>641460</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>659104</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>685844</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>676406</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>694353</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1323365</t>
+          <t>1322894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1348648</t>
+          <t>1347933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6931</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12760</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6072</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2838</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10870</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2790</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11022</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,62%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6931</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3734</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12150</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>79261</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73432</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82959</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>85670</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>80872</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88904</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>80720</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>88952</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,38%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>79261</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>74042</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82458</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158269</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169562</t>
+          <t>170119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91742</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91742</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91742</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33681</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24839</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43786</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24046</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16179</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31954</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17254</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33144</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,32%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>26414</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>45703</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46037</t>
+          <t>45771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>69984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>457690</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>447585</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>466532</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>620</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>427582</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>419674</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>435449</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>418484</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>434374</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>457690</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>445668</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>464957</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>872213</t>
+          <t>873016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896963</t>
+          <t>897229</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>491371</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>491371</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>491371</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>451628</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>451628</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>451628</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>491371</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>491371</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>491371</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5488</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2436</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8503</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14098</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14876</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,1%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5488</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11433</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>21660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166740</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>161400</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>169792</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>158309</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152714</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>162276</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151936</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>161947</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166740</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>169906</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317820</t>
+          <t>317381</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330437</t>
+          <t>329965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35863</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>58838</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>38621</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29857</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50555</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>29760</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50695</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>46100</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36085</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>58002</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70412</t>
+          <t>70134</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100300</t>
+          <t>100819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>703692</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>690954</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>713929</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>968</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>671561</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>659627</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>680325</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>659487</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>680422</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>703692</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>691790</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>713707</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1359674</t>
+          <t>1359155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1389562</t>
+          <t>1389840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>749792</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>749792</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>749792</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>710182</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>710182</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>710182</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>749792</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>749792</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>749792</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,67 +3934,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2239</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2084</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6018</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5532</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2239</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5954</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66375</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61999</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67943</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57294</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53360</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>58849</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>53846</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58842</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66375</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62660</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67948</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119030</t>
+          <t>118448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126283</t>
+          <t>125986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23918</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17334</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32911</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>23797</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17524</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32113</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17161</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32291</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23918</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>16957</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32849</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38543</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59805</t>
+          <t>60338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>464817</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>455824</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>471401</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>677</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>448493</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>440177</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>454766</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>439999</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>455129</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>464817</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>455886</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>471778</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>901220</t>
+          <t>900687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>922482</t>
+          <t>923259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6729</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12619</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11184</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6921</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17674</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6926</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17041</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>4,01%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6729</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3142</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12250</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>26148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>180766</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>174876</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>183938</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>161519</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>155029</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>165782</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>155662</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>165777</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,13%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>95,99%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>180766</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>175245</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>184353</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,47%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>503</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334719</t>
+          <t>334049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>348181</t>
+          <t>348129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24341</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43080</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37065</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28561</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>47171</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28392</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>46841</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>32886</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>24044</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>43119</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83620</t>
+          <t>86489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>711958</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>701764</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>720503</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>667306</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>657200</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>675810</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>657530</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>675979</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>711958</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>701725</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>720800</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1365595</t>
+          <t>1362726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1391600</t>
+          <t>1390598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12339</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4901</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2326</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9678</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49830</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44393</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53202</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>49777</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45000</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52352</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54906</t>
+          <t>42155</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49166</t>
+          <t>38077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>44581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>104683</t>
+          <t>91985</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>85487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109680</t>
+          <t>96516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27410</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19465</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36701</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22546</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14729</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31219</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21305</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>29726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65039</t>
+          <t>61502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>448268</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>438977</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>456213</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>437148</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>428475</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>444965</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>487003</t>
+          <t>409726</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475913</t>
+          <t>401876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495314</t>
+          <t>416285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>924151</t>
+          <t>857994</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911274</t>
+          <t>845778</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935391</t>
+          <t>868155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>11321</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>30906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -6331,67 +6331,67 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161197</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>139560</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>132676</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>143508</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>170922</t>
+          <t>139679</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163839</t>
+          <t>133455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175734</t>
+          <t>144325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>310483</t>
+          <t>296240</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301325</t>
+          <t>286952</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317098</t>
+          <t>302726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45633</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35761</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>58317</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>37437</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27808</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>48328</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>27749</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61482</t>
+          <t>47568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>67829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103061</t>
+          <t>98519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>654660</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>641976</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>664532</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>883</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>626486</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>615595</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>636115</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>712831</t>
+          <t>591559</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>699766</t>
+          <t>580768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>723830</t>
+          <t>600587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1339317</t>
+          <t>1246220</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1322110</t>
+          <t>1230110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1354107</t>
+          <t>1260800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
